--- a/result/R107_Test.xlsx
+++ b/result/R107_Test.xlsx
@@ -449,16 +449,16 @@
         <v>1</v>
       </c>
       <c r="B4" s="3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>1203.9</v>
+        <v>0</v>
       </c>
       <c r="D4" s="3">
-        <v>1203.9</v>
+        <v>0</v>
       </c>
       <c r="E4" s="3">
-        <v>98.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -466,16 +466,16 @@
         <v>7</v>
       </c>
       <c r="B5" s="3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>1203.9</v>
+        <v>0</v>
       </c>
       <c r="D5" s="3">
-        <v>1203.9</v>
+        <v>0</v>
       </c>
       <c r="E5" s="3">
-        <v>98.67</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
